--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -9,10 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24042" windowHeight="9617"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24042" windowHeight="9617" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="Register" sheetId="2" r:id="rId2"/>
+    <sheet name="UserProfile" sheetId="3" r:id="rId3"/>
+    <sheet name="Search" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>email</t>
   </si>
@@ -47,19 +50,85 @@
     <t>invalid</t>
   </si>
   <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>account</t>
-  </si>
-  <si>
     <t>Abc12344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description </t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>Sai mật khẩu</t>
+  </si>
+  <si>
+    <t>Email đúng, trống</t>
+  </si>
+  <si>
+    <t>Email trống, mật khẩu đúng</t>
+  </si>
+  <si>
+    <t>fullname</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>123 Test Street</t>
+  </si>
+  <si>
+    <t>Cập nhật địa chỉ thành công</t>
+  </si>
+  <si>
+    <t>keyword</t>
+  </si>
+  <si>
+    <t>expectedResult</t>
+  </si>
+  <si>
+    <t>rtx 2050</t>
+  </si>
+  <si>
+    <t>&gt;0</t>
+  </si>
+  <si>
+    <t>Tìm sản phẩm có kết quả</t>
+  </si>
+  <si>
+    <t>@#$%</t>
+  </si>
+  <si>
+    <t>Ký tự đặc biệt, không có kết quả</t>
+  </si>
+  <si>
+    <t>Exist User</t>
+  </si>
+  <si>
+    <t>new@test.com</t>
+  </si>
+  <si>
+    <t>Short Pass</t>
+  </si>
+  <si>
+    <t>Email đã tồn tại</t>
+  </si>
+  <si>
+    <t>Mật khẩu quá ngắn</t>
+  </si>
+  <si>
+    <t>456 Main Road</t>
+  </si>
+  <si>
+    <t>laptop</t>
+  </si>
+  <si>
+    <t>Tìm sản phẩm laptop</t>
+  </si>
+  <si>
+    <t>Không nhập địa chỉ</t>
   </si>
 </sst>
 </file>
@@ -118,7 +187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -141,12 +210,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -161,6 +243,22 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -458,7 +556,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -473,8 +571,8 @@
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -488,7 +586,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -502,7 +600,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -512,12 +610,12 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="2"/>
@@ -540,4 +638,250 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="25.5546875" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.65" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.65" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="8">
+        <v>12</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2" display="vscode-file://vscode-app/c:/Users/tranp/AppData/Local/Programs/Microsoft VS Code/resources/app/out/vs/code/electron-browser/workbench/workbench.html"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.65" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="36.35" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36.35" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30.7" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="24.45" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="36.35" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="36.35" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="36.35" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.65" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>